--- a/Prestador/prontobaby/resultado/relatorio_prontobaby_COMPLETO.xlsx
+++ b/Prestador/prontobaby/resultado/relatorio_prontobaby_COMPLETO.xlsx
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -677,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
